--- a/r4-ELGA-AustrianPatientSummary-main/StructureDefinition-at-aps-patient.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-main/StructureDefinition-at-aps-patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-21T10:23:38+00:00</t>
+    <t>2025-02-24T13:55:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-AustrianPatientSummary-main/StructureDefinition-at-aps-patient.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-main/StructureDefinition-at-aps-patient.xlsx
@@ -48,7 +48,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>draft</t>
+    <t>active</t>
   </si>
   <si>
     <t>Experimental</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-24T13:55:23+00:00</t>
+    <t>2025-02-26T08:56:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-AustrianPatientSummary-main/StructureDefinition-at-aps-patient.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-main/StructureDefinition-at-aps-patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-26T08:56:44+00:00</t>
+    <t>2025-03-04T11:06:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -642,7 +642,7 @@
   </si>
   <si>
     <t>HL7® Austria FHIR® Core Extension for the religion (registered in Austria) of a patient.
-The extension is used to encode the religious confession of a patient (only confessions registered in Austria). Furthermore, it uses the official [HL7 AT CodeSystem](https://build.fhir.org/ig/HL7Austria/HL7-AT-FHIR-Core-R4/https://termpub.gesundheit.gv.at:443/TermBrowser/gui/main/main.zul?loadType=CodeSystem&amp;loadName=HL7 AT ReligionAustria) for religion and is therefore aligned with the ELGA ValueSet, respectively.</t>
+The extension is used to encode the religious confession of a patient (only confessions registered in Austria). Furthermore, it uses the official [HL7 AT CodeSystem](http://hl7.at/fhir/HL7ATCoreProfiles/4.0.1/2.0.0/https://termpub.gesundheit.gv.at:443/TermBrowser/gui/main/main.zul?loadType=CodeSystem&amp;loadName=HL7 AT ReligionAustria) for religion and is therefore aligned with the ELGA ValueSet, respectively.</t>
   </si>
   <si>
     <t>Patient.extension:birthPlace</t>

--- a/r4-ELGA-AustrianPatientSummary-main/StructureDefinition-at-aps-patient.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-main/StructureDefinition-at-aps-patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-04T11:06:18+00:00</t>
+    <t>2025-03-06T12:24:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-AustrianPatientSummary-main/StructureDefinition-at-aps-patient.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-main/StructureDefinition-at-aps-patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-06T12:24:43+00:00</t>
+    <t>2025-03-20T12:28:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-AustrianPatientSummary-main/StructureDefinition-at-aps-patient.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-main/StructureDefinition-at-aps-patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-20T12:28:15+00:00</t>
+    <t>2025-03-24T06:28:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-AustrianPatientSummary-main/StructureDefinition-at-aps-patient.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-main/StructureDefinition-at-aps-patient.xlsx
@@ -24,7 +24,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>https://fhir.hl7.at/elga-austrianpatientsummary-r4/StructureDefinition/at-aps-patient</t>
+    <t>https://fhir.hl7.at/elga/aps/r4/StructureDefinition/at-aps-patient</t>
   </si>
   <si>
     <t>Version</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-24T06:28:05+00:00</t>
+    <t>2025-03-24T07:27:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-AustrianPatientSummary-main/StructureDefinition-at-aps-patient.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-main/StructureDefinition-at-aps-patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-24T07:27:46+00:00</t>
+    <t>2025-03-24T07:43:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-AustrianPatientSummary-main/StructureDefinition-at-aps-patient.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-main/StructureDefinition-at-aps-patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-11-18T10:23:29+00:00</t>
+    <t>2026-01-28T10:05:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -3037,7 +3037,7 @@
     <t>Patient.link.other</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Patient|RelatedPerson)
+    <t xml:space="preserve">Reference(https://fhir.hl7.at/elga/aps/r4/StructureDefinition/at-aps-patient|RelatedPerson)
 </t>
   </si>
   <si>

--- a/r4-ELGA-AustrianPatientSummary-main/StructureDefinition-at-aps-patient.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-main/StructureDefinition-at-aps-patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-28T10:05:57+00:00</t>
+    <t>2026-01-29T06:33:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-AustrianPatientSummary-main/StructureDefinition-at-aps-patient.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-main/StructureDefinition-at-aps-patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-29T06:33:09+00:00</t>
+    <t>2026-02-03T10:06:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-AustrianPatientSummary-main/StructureDefinition-at-aps-patient.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-main/StructureDefinition-at-aps-patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-03T10:34:36+00:00</t>
+    <t>2026-02-09T07:50:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,7 +84,10 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Das AT APS-Profil für die Patient-Ressource ist vom entsprechenden Profil aus dem HL7® Austria FHIR® Core IG abgeleitet und stellt zusätzlich die Konformität gegenüber dem IPS-Profil sicher, indem die so genannte [`imposeProfile`](http://hl7.org/fhir/StructureDefinition/structuredefinition-imposeProfile)-Erweiterung verwendet wird.</t>
+    <t>Patientendaten, inkl. Angabe von Kontaktpersonen, Hausarzt bzw. primäre Ansprechpartner.
+Um die Vorgaben aus dem Umfeld von MyHealth@EU zu erfüllen, muss ein Vor- und Nachname angegeben werden.
+Das AT APS-Profil für die Patient-Ressource ist vom entsprechenden Profil aus dem HL7® Austria FHIR® Core IG abgeleitet und stellt zusätzlich die Konformität gegenüber dem IPS-Profil sicher, indem die so genannte [`imposeProfile`](http://hl7.org/fhir/StructureDefinition/structuredefinition-imposeProfile)-Erweiterung verwendet wird. 
+Deshalb ist die Angabe des Geburtsdatums erforderlich.</t>
   </si>
   <si>
     <t>Purpose</t>

--- a/r4-ELGA-AustrianPatientSummary-main/StructureDefinition-at-aps-patient.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-main/StructureDefinition-at-aps-patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-09T07:50:08+00:00</t>
+    <t>2026-02-13T12:44:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-AustrianPatientSummary-main/StructureDefinition-at-aps-patient.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-main/StructureDefinition-at-aps-patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-13T12:44:21+00:00</t>
+    <t>2026-02-16T08:31:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -465,7 +465,7 @@
     <t>citizenship</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {patient-citizenship}
+    <t xml:space="preserve">Extension {patient-citizenship|5.2.0}
 </t>
   </si>
   <si>
@@ -657,7 +657,7 @@
     <t>birthPlace</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {patient-birthPlace}
+    <t xml:space="preserve">Extension {patient-birthPlace|5.2.0}
 </t>
   </si>
   <si>
@@ -2142,7 +2142,7 @@
     <t>street</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {iso21090-ADXP-streetName}
+    <t xml:space="preserve">Extension {iso21090-ADXP-streetName|5.2.0}
 </t>
   </si>
   <si>
@@ -2161,7 +2161,7 @@
     <t>streetNumber</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {iso21090-ADXP-houseNumber}
+    <t xml:space="preserve">Extension {iso21090-ADXP-houseNumber|5.2.0}
 </t>
   </si>
   <si>
@@ -2180,7 +2180,7 @@
     <t>floorDoorNumber</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {iso21090-ADXP-additionalLocator}
+    <t xml:space="preserve">Extension {iso21090-ADXP-additionalLocator|5.2.0}
 </t>
   </si>
   <si>

--- a/r4-ELGA-AustrianPatientSummary-main/StructureDefinition-at-aps-patient.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-main/StructureDefinition-at-aps-patient.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.2.0</t>
+    <t>1.0.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-16T08:31:54+00:00</t>
+    <t>2026-02-16T11:13:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-AustrianPatientSummary-main/StructureDefinition-at-aps-patient.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-main/StructureDefinition-at-aps-patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-16T11:13:42+00:00</t>
+    <t>2026-02-17T09:00:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-AustrianPatientSummary-main/StructureDefinition-at-aps-patient.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-main/StructureDefinition-at-aps-patient.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.0.0</t>
+    <t>1.1.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-17T09:00:43+00:00</t>
+    <t>2026-09-01T07:40:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -465,7 +465,7 @@
     <t>citizenship</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {patient-citizenship|5.2.0}
+    <t xml:space="preserve">Extension {patient-citizenship|5.3.0}
 </t>
   </si>
   <si>
@@ -657,7 +657,7 @@
     <t>birthPlace</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {patient-birthPlace|5.2.0}
+    <t xml:space="preserve">Extension {patient-birthPlace|5.3.0}
 </t>
   </si>
   <si>
@@ -2142,7 +2142,7 @@
     <t>street</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {iso21090-ADXP-streetName|5.2.0}
+    <t xml:space="preserve">Extension {iso21090-ADXP-streetName|5.3.0}
 </t>
   </si>
   <si>
@@ -2161,7 +2161,7 @@
     <t>streetNumber</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {iso21090-ADXP-houseNumber|5.2.0}
+    <t xml:space="preserve">Extension {iso21090-ADXP-houseNumber|5.3.0}
 </t>
   </si>
   <si>
@@ -2180,7 +2180,7 @@
     <t>floorDoorNumber</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {iso21090-ADXP-additionalLocator|5.2.0}
+    <t xml:space="preserve">Extension {iso21090-ADXP-additionalLocator|5.3.0}
 </t>
   </si>
   <si>
